--- a/experiment/SRForm2_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/SRForm2_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.95</v>
+        <v>22.97</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5255</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.88</v>
+        <v>25.91</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.36</v>
+        <v>25.34</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6351</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.36</v>
+        <v>26.37</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5782</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.18</v>
+        <v>23.26</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7125</v>
+        <v>0.7181</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.83</v>
+        <v>32.87</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7925</v>
+        <v>0.7936</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.87</v>
+        <v>28.01</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8071</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.52</v>
+        <v>33.47</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9169</v>
+        <v>0.9177</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.19</v>
+        <v>32.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8606</v>
+        <v>0.8609</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.27</v>
+        <v>27.29</v>
       </c>
       <c r="C11" t="n">
-        <v>0.747</v>
+        <v>0.7475000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.26</v>
+        <v>32.41</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9398</v>
+        <v>0.9416</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.92</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8772</v>
+        <v>0.8778</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.09</v>
+        <v>26.22</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9388</v>
+        <v>0.9408</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.13</v>
+        <v>27.19</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7739</v>
+        <v>0.7732</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.34</v>
+        <v>28.39</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7751</v>
+        <v>0.7766999999999999</v>
       </c>
     </row>
   </sheetData>
